--- a/product-definitions/spreadsheet/aerosol-backscatter.xlsx
+++ b/product-definitions/spreadsheet/aerosol-backscatter.xlsx
@@ -314,7 +314,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -351,11 +351,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
@@ -386,7 +381,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -418,7 +413,7 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
@@ -428,23 +423,22 @@
     <xf borderId="0" fillId="0" fontId="6" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="11" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="11" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
@@ -3010,7 +3004,7 @@
       <c r="C13" s="9"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="11" t="s">
         <v>53</v>
       </c>
     </row>
@@ -3043,7 +3037,7 @@
         <v>41</v>
       </c>
       <c r="C18" s="13"/>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="11" t="s">
         <v>53</v>
       </c>
     </row>
@@ -3059,27 +3053,27 @@
       <c r="B20" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="18">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="B21" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="B22" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="B23" s="11" t="s">
         <v>58</v>
       </c>
@@ -3087,7 +3081,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="B24" s="11" t="s">
         <v>51</v>
       </c>
@@ -3095,16 +3089,16 @@
         <v>52</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="C25" s="13"/>
     </row>
-    <row r="26">
-      <c r="A26" s="18" t="s">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="11" t="s">
         <v>60</v>
       </c>
       <c r="C26" s="13"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="B27" s="11" t="s">
         <v>38</v>
       </c>
@@ -3112,7 +3106,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="B28" s="11" t="s">
         <v>40</v>
       </c>
@@ -3120,56 +3114,56 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="B29" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="20">
+      <c r="C29" s="19">
         <v>1.0</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="B30" s="11" t="s">
         <v>41</v>
       </c>
       <c r="C30" s="13"/>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="B31" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="11" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="B32" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="18">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="B33" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="B34" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="B35" s="11" t="s">
         <v>58</v>
       </c>
@@ -3177,7 +3171,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="B36" s="11" t="s">
         <v>51</v>
       </c>
@@ -3185,16 +3179,16 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="C37" s="13"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="11" t="s">
         <v>62</v>
       </c>
       <c r="C38" s="13"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="B39" s="11" t="s">
         <v>38</v>
       </c>
@@ -3202,7 +3196,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="B40" s="11" t="s">
         <v>40</v>
       </c>
@@ -3210,7 +3204,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="B41" s="11" t="s">
         <v>29</v>
       </c>
@@ -3218,7 +3212,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="B42" s="11" t="s">
         <v>41</v>
       </c>
@@ -3227,7 +3221,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="B43" s="11" t="s">
         <v>42</v>
       </c>
@@ -3235,31 +3229,31 @@
         <v>65</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="B44" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C44" s="19">
+      <c r="C44" s="18">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="B45" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="19" t="s">
+      <c r="C45" s="18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="B46" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C46" s="19" t="s">
+      <c r="C46" s="18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="B47" s="11" t="s">
         <v>58</v>
       </c>
@@ -3267,7 +3261,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="B48" s="11" t="s">
         <v>51</v>
       </c>
@@ -3275,13 +3269,14 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50">
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="11" t="s">
         <v>66</v>
       </c>
       <c r="C50" s="13"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="B51" s="11" t="s">
         <v>38</v>
       </c>
@@ -3289,7 +3284,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="B52" s="11" t="s">
         <v>40</v>
       </c>
@@ -3297,7 +3292,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="B53" s="11" t="s">
         <v>29</v>
       </c>
@@ -3305,7 +3300,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="B54" s="11" t="s">
         <v>41</v>
       </c>
@@ -3314,7 +3309,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="B55" s="11" t="s">
         <v>42</v>
       </c>
@@ -3322,31 +3317,31 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="B56" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C56" s="19">
+      <c r="C56" s="18">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="B57" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C57" s="21" t="s">
+      <c r="C57" s="20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="B58" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C58" s="21" t="s">
+      <c r="C58" s="20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="B59" s="11" t="s">
         <v>58</v>
       </c>
@@ -3354,7 +3349,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="B60" s="11" t="s">
         <v>51</v>
       </c>
@@ -3362,13 +3357,14 @@
         <v>52</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="18" t="s">
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="11" t="s">
         <v>69</v>
       </c>
       <c r="C62" s="13"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="B63" s="11" t="s">
         <v>38</v>
       </c>
@@ -3376,7 +3372,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="B64" s="11" t="s">
         <v>40</v>
       </c>
@@ -3384,7 +3380,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="B65" s="11" t="s">
         <v>29</v>
       </c>
@@ -3392,15 +3388,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="B66" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C66" s="18" t="s">
+      <c r="C66" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="B67" s="11" t="s">
         <v>42</v>
       </c>
@@ -3408,31 +3404,31 @@
         <v>71</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="B68" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C68" s="19">
+      <c r="C68" s="18">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="B69" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C69" s="21" t="s">
+      <c r="C69" s="20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="B70" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C70" s="21" t="s">
+      <c r="C70" s="20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="B71" s="11" t="s">
         <v>58</v>
       </c>
@@ -3440,7 +3436,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="B72" s="11" t="s">
         <v>51</v>
       </c>
@@ -3448,13 +3444,14 @@
         <v>52</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="18" t="s">
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="11" t="s">
         <v>72</v>
       </c>
       <c r="C74" s="13"/>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="B75" s="11" t="s">
         <v>38</v>
       </c>
@@ -3462,7 +3459,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="B76" s="11" t="s">
         <v>40</v>
       </c>
@@ -3470,7 +3467,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="B77" s="11" t="s">
         <v>29</v>
       </c>
@@ -3478,15 +3475,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="B78" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="18" t="s">
+      <c r="C78" s="11" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="B79" s="11" t="s">
         <v>42</v>
       </c>
@@ -3494,31 +3491,31 @@
         <v>73</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="B80" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C80" s="19">
+      <c r="C80" s="18">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="B81" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C81" s="21" t="s">
+      <c r="C81" s="20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="B82" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C82" s="21" t="s">
+      <c r="C82" s="20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="B83" s="11" t="s">
         <v>58</v>
       </c>
@@ -3526,7 +3523,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="B84" s="11" t="s">
         <v>51</v>
       </c>
@@ -3534,13 +3531,14 @@
         <v>52</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="18" t="s">
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="11" t="s">
         <v>74</v>
       </c>
       <c r="C86" s="13"/>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="B87" s="11" t="s">
         <v>38</v>
       </c>
@@ -3548,7 +3546,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="B88" s="11" t="s">
         <v>40</v>
       </c>
@@ -3556,20 +3554,20 @@
         <v>63</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="B89" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C89" s="20">
+      <c r="C89" s="19">
         <v>1.0</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="B90" s="11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="B91" s="11" t="s">
         <v>42</v>
       </c>
@@ -3577,31 +3575,31 @@
         <v>75</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="B92" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C92" s="19">
+      <c r="C92" s="18">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="B93" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C93" s="21" t="s">
+      <c r="C93" s="20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="B94" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C94" s="21" t="s">
+      <c r="C94" s="20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="B95" s="11" t="s">
         <v>58</v>
       </c>
@@ -3609,7 +3607,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="B96" s="11" t="s">
         <v>51</v>
       </c>
@@ -3617,13 +3615,14 @@
         <v>52</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="18" t="s">
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="11" t="s">
         <v>77</v>
       </c>
       <c r="C98" s="13"/>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="B99" s="11" t="s">
         <v>38</v>
       </c>
@@ -3631,7 +3630,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="B100" s="11" t="s">
         <v>40</v>
       </c>
@@ -3639,20 +3638,20 @@
         <v>63</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="B101" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C101" s="20" t="s">
+      <c r="C101" s="19" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="B102" s="11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="B103" s="11" t="s">
         <v>42</v>
       </c>
@@ -3660,31 +3659,31 @@
         <v>78</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="B104" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C104" s="19">
+      <c r="C104" s="18">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="B105" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C105" s="21" t="s">
+      <c r="C105" s="20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="B106" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C106" s="21" t="s">
+      <c r="C106" s="20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="B107" s="11" t="s">
         <v>58</v>
       </c>
@@ -3692,7 +3691,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="B108" s="11" t="s">
         <v>51</v>
       </c>
@@ -3700,13 +3699,14 @@
         <v>52</v>
       </c>
     </row>
-    <row r="110">
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C110" s="13"/>
     </row>
-    <row r="111">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="B111" s="11" t="s">
         <v>38</v>
       </c>
@@ -3714,7 +3714,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="B112" s="11" t="s">
         <v>40</v>
       </c>
@@ -3722,15 +3722,15 @@
         <v>63</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="B113" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C113" s="20" t="s">
+      <c r="C113" s="19" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="B114" s="11" t="s">
         <v>41</v>
       </c>
@@ -3739,7 +3739,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="B115" s="11" t="s">
         <v>42</v>
       </c>
@@ -3747,31 +3747,31 @@
         <v>82</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="B116" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C116" s="19">
+      <c r="C116" s="18">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="B117" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C117" s="21" t="s">
+      <c r="C117" s="20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="B118" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C118" s="21" t="s">
+      <c r="C118" s="20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="B119" s="11" t="s">
         <v>58</v>
       </c>
@@ -3779,7 +3779,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="B120" s="11" t="s">
         <v>51</v>
       </c>
@@ -3787,13 +3787,14 @@
         <v>52</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="18" t="s">
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="11" t="s">
         <v>83</v>
       </c>
       <c r="C122" s="13"/>
     </row>
-    <row r="123">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="B123" s="11" t="s">
         <v>38</v>
       </c>
@@ -3801,7 +3802,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="B124" s="11" t="s">
         <v>40</v>
       </c>
@@ -3809,21 +3810,21 @@
         <v>63</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="B125" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C125" s="20" t="s">
+      <c r="C125" s="19" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="B126" s="11" t="s">
         <v>41</v>
       </c>
       <c r="C126" s="13"/>
     </row>
-    <row r="127">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="B127" s="11" t="s">
         <v>42</v>
       </c>
@@ -3831,31 +3832,31 @@
         <v>84</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="B128" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C128" s="19">
+      <c r="C128" s="18">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="B129" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C129" s="21" t="s">
+      <c r="C129" s="20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" ht="15.75" customHeight="1">
       <c r="B130" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C130" s="21" t="s">
+      <c r="C130" s="20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="B131" s="11" t="s">
         <v>58</v>
       </c>
@@ -3863,7 +3864,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="B132" s="11" t="s">
         <v>51</v>
       </c>
@@ -3871,13 +3872,14 @@
         <v>52</v>
       </c>
     </row>
-    <row r="134">
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="11" t="s">
         <v>85</v>
       </c>
       <c r="C134" s="13"/>
     </row>
-    <row r="135">
+    <row r="135" ht="15.75" customHeight="1">
       <c r="B135" s="11" t="s">
         <v>38</v>
       </c>
@@ -3885,7 +3887,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" ht="15.75" customHeight="1">
       <c r="B136" s="11" t="s">
         <v>40</v>
       </c>
@@ -3893,15 +3895,15 @@
         <v>63</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" ht="15.75" customHeight="1">
       <c r="B137" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C137" s="20" t="s">
+      <c r="C137" s="19" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" ht="15.75" customHeight="1">
       <c r="B138" s="11" t="s">
         <v>41</v>
       </c>
@@ -3910,39 +3912,39 @@
         <v>85</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" ht="15.75" customHeight="1">
       <c r="B139" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C139" s="18" t="s">
+      <c r="C139" s="11" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" ht="15.75" customHeight="1">
       <c r="B140" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C140" s="19">
+      <c r="C140" s="18">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="B141" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C141" s="21" t="s">
+      <c r="C141" s="20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" ht="15.75" customHeight="1">
       <c r="B142" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C142" s="21" t="s">
+      <c r="C142" s="20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" ht="15.75" customHeight="1">
       <c r="B143" s="11" t="s">
         <v>58</v>
       </c>
@@ -3950,7 +3952,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" ht="15.75" customHeight="1">
       <c r="B144" s="11" t="s">
         <v>51</v>
       </c>
@@ -3958,13 +3960,14 @@
         <v>52</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="18" t="s">
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1">
+      <c r="A146" s="11" t="s">
         <v>87</v>
       </c>
       <c r="C146" s="13"/>
     </row>
-    <row r="147">
+    <row r="147" ht="15.75" customHeight="1">
       <c r="B147" s="11" t="s">
         <v>38</v>
       </c>
@@ -3972,7 +3975,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" ht="15.75" customHeight="1">
       <c r="B148" s="11" t="s">
         <v>40</v>
       </c>
@@ -3980,53 +3983,53 @@
         <v>63</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" ht="15.75" customHeight="1">
       <c r="B149" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C149" s="20" t="s">
+      <c r="C149" s="19" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" ht="15.75" customHeight="1">
       <c r="B150" s="11" t="s">
         <v>41</v>
       </c>
       <c r="C150" s="13"/>
     </row>
-    <row r="151">
+    <row r="151" ht="15.75" customHeight="1">
       <c r="B151" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C151" s="18" t="s">
+      <c r="C151" s="11" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" ht="15.75" customHeight="1">
       <c r="B152" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C152" s="19">
+      <c r="C152" s="18">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" ht="15.75" customHeight="1">
       <c r="B153" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C153" s="21" t="s">
+      <c r="C153" s="20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" ht="15.75" customHeight="1">
       <c r="B154" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C154" s="21" t="s">
+      <c r="C154" s="20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" ht="15.75" customHeight="1">
       <c r="B155" s="11" t="s">
         <v>58</v>
       </c>
@@ -4034,7 +4037,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" ht="15.75" customHeight="1">
       <c r="B156" s="11" t="s">
         <v>51</v>
       </c>
@@ -4042,13 +4045,14 @@
         <v>52</v>
       </c>
     </row>
-    <row r="158">
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="11" t="s">
         <v>90</v>
       </c>
       <c r="C158" s="13"/>
     </row>
-    <row r="159">
+    <row r="159" ht="15.75" customHeight="1">
       <c r="B159" s="11" t="s">
         <v>38</v>
       </c>
@@ -4056,7 +4060,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" ht="15.75" customHeight="1">
       <c r="B160" s="11" t="s">
         <v>40</v>
       </c>
@@ -4064,21 +4068,21 @@
         <v>54</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" ht="15.75" customHeight="1">
       <c r="B161" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C161" s="20">
+      <c r="C161" s="19">
         <v>1.0</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" ht="15.75" customHeight="1">
       <c r="B162" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C162" s="20"/>
-    </row>
-    <row r="163">
+      <c r="C162" s="19"/>
+    </row>
+    <row r="163" ht="15.75" customHeight="1">
       <c r="B163" s="11" t="s">
         <v>42</v>
       </c>
@@ -4086,7 +4090,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" ht="15.75" customHeight="1">
       <c r="B164" s="3" t="s">
         <v>93</v>
       </c>
@@ -4094,11 +4098,11 @@
         <v>94</v>
       </c>
     </row>
-    <row r="165">
-      <c r="B165" s="22" t="s">
+    <row r="165" ht="15.75" customHeight="1">
+      <c r="B165" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="C165" s="23" t="s">
+      <c r="C165" s="22" t="s">
         <v>96</v>
       </c>
     </row>
